--- a/AcompanhamentoFaturados.xlsx
+++ b/AcompanhamentoFaturados.xlsx
@@ -8,22 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PedroMencariniGarcia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{B615E9F5-4E4B-49A6-9628-E103351D5368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCD3AB15-474B-4ABC-83CD-FB096B9AFF74}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE5E38F-0C2A-4A17-9871-4DF9787BF6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contatos" sheetId="5" r:id="rId1"/>
     <sheet name="Mesclado" sheetId="1" r:id="rId2"/>
-    <sheet name="21_09" sheetId="2" r:id="rId3"/>
-    <sheet name="22_09" sheetId="4" r:id="rId4"/>
-    <sheet name="SETEMBRO_2026" sheetId="3" r:id="rId5"/>
+    <sheet name="Monitor" sheetId="7" r:id="rId3"/>
+    <sheet name="21_09" sheetId="2" r:id="rId4"/>
+    <sheet name="22_09" sheetId="4" r:id="rId5"/>
+    <sheet name="23_09" sheetId="6" r:id="rId6"/>
+    <sheet name="SETEMBRO_2026" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'21_09'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'21_09'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'22_09'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Contatos!$A$1:$F$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mesclado!$A$1:$H$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Contatos!$A$1:$F$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'22_09'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'23_09'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Monitor!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="297">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -480,6 +484,294 @@
     <t>-</t>
   </si>
   <si>
+    <t>DIRETÓRIOS</t>
+  </si>
+  <si>
+    <t>DIRETÓRIOS BADS</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\EQUATORIAL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Imobiliario\DIARIO</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Mais</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Star Companies</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SULAMERICA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Swile</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Tokio</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\TS Serviços\Sicredi Conver01</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\TS Serviços\TS Serviços</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Yamaha Banco</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AMIL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\AMIL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Assegurou</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Assegurou</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AXA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\AXA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Banestes</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Banestes</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Berlanda</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Berlanda</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Brasil Cap</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Brasil_Cap</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Captalizacao</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Capitalizacao</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Centauro</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Centauro</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\CNP</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\CNP</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Crefisa</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Crefisa_Seguros</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Daycoval</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Daycoval</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Efeito</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Efeito</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\FATUREEPAGUE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\FATUREEPAGUE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Hecsolutions</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Hecsolutions</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Hellomed</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Hellomed</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Incentive</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Incentive</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\INTEGRITY</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Integrity</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Kapam</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\KAPAM</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\KOVRPICPAY</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Kovrpicpay</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\LMMOBILIDADE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\LMMOBILIDADE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AEGON\COLETIVO</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAG_Coletivo</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AEGON\MAG_VIDA_INDIVIDUAL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAG_Individual</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Auto_+_Casa\BB</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_Auto_+_Casa\BB</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Auto_+_Casa\Mapfre</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_Auto_+_Casa\MAPFRE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\BV</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_BV</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Educacional\DIARIO</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_EDUCACIONAL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre Favela</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Mapfre_Favela</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Vida Seguradora</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_Vida_Seguradora</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mentore</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Mentore</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\METLIFE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Metlife</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Naturgy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Naturgy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\NOSSA_CAIXA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Nossa_Caixa</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Oxxy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Oxxy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Psicologica</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\PSICOLOGICA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Ramos Elementares</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Ramos_Elementares</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SAUDAPP</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Saudapp</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SENFF</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Senff</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Sicoob</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Sicoob</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Sura</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Sura</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\USADOSBR</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\USADOSBR</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\USEDIGI</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\USEDIGI</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Vaticano</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Vaticano</t>
+  </si>
+  <si>
     <t>FREQUENCIA</t>
   </si>
   <si>
@@ -522,292 +814,133 @@
     <t>BAD</t>
   </si>
   <si>
-    <t>DIRETÓRIOS</t>
-  </si>
-  <si>
-    <t>DIRETÓRIOS BADS</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AEGON\COLETIVO</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAG_Coletivo</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AEGON\MAG_VIDA_INDIVIDUAL</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAG_Individual</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AMIL</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\AMIL</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Assegurou</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Assegurou</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Auto_+_Casa\BB</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAPFRE_Auto_+_Casa\BB</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Auto_+_Casa\Mapfre</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAPFRE_Auto_+_Casa\MAPFRE</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AXA</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\AXA</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Banestes</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Banestes</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Berlanda</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Berlanda</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Brasil Cap</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Brasil_Cap</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Centauro</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Centauro</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\CNP</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\CNP</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Crefisa</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Crefisa_Seguros</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Daycoval</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Daycoval</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Efeito</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Efeito</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\EQUATORIAL</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\FATUREEPAGUE</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\FATUREEPAGUE</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Hecsolutions</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Hecsolutions</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Hellomed</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Hellomed</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Incentive</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Incentive</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\INTEGRITY</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Integrity</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Kapam</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\KAPAM</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\KOVRPICPAY</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Kovrpicpay</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\LMMOBILIDADE</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\LMMOBILIDADE</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Educacional\DIARIO</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAPFRE_EDUCACIONAL</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre Favela</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Mapfre_Favela</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Imobiliario\DIARIO</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Mais</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\BV</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAPFRE_BV</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Captalizacao</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Capitalizacao</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Psicologica</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\PSICOLOGICA</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Vida Seguradora</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\MAPFRE_Vida_Seguradora</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mentore</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Mentore</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\METLIFE</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Metlife</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Naturgy</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Naturgy</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\NOSSA_CAIXA</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Nossa_Caixa</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Oxxy</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Oxxy</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Ramos Elementares</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Ramos_Elementares</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SAUDAPP</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Saudapp</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SENFF</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Senff</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Sicoob</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Sicoob</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Star Companies</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SULAMERICA</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Sura</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Sura</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Swile</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Tokio</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\TS Serviços\Sicredi Conver01</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\TS Serviços\TS Serviços</t>
-  </si>
-  <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\USADOSBR</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\USADOSBR</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\USEDIGI</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\USEDIGI</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Vaticano</t>
-  </si>
-  <si>
     <t>Z:\_BKP Erros\Vaticano</t>
   </si>
   <si>
-    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Yamaha Banco</t>
+    <t xml:space="preserve">PENDENTE ARQUIVO </t>
   </si>
 </sst>
 </file>
@@ -817,7 +950,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,6 +963,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -898,10 +1039,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -916,17 +1058,28 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -4441,6 +4594,1386 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44886F52-D7D0-4D08-B2D7-D1AD344D9EAF}">
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="89" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" t="s">
+        <v>162</v>
+      </c>
+      <c r="H16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" t="s">
+        <v>184</v>
+      </c>
+      <c r="H27" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" t="s">
+        <v>188</v>
+      </c>
+      <c r="H29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" t="s">
+        <v>190</v>
+      </c>
+      <c r="H30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" t="s">
+        <v>200</v>
+      </c>
+      <c r="H35" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" t="s">
+        <v>202</v>
+      </c>
+      <c r="H36" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" t="s">
+        <v>204</v>
+      </c>
+      <c r="H37" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" t="s">
+        <v>206</v>
+      </c>
+      <c r="H38" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" t="s">
+        <v>214</v>
+      </c>
+      <c r="H42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" t="s">
+        <v>216</v>
+      </c>
+      <c r="H43" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" t="s">
+        <v>218</v>
+      </c>
+      <c r="H44" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" t="s">
+        <v>220</v>
+      </c>
+      <c r="H45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" t="s">
+        <v>222</v>
+      </c>
+      <c r="H46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" t="s">
+        <v>224</v>
+      </c>
+      <c r="H47" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" t="s">
+        <v>226</v>
+      </c>
+      <c r="H48" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" t="s">
+        <v>228</v>
+      </c>
+      <c r="H49" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" t="s">
+        <v>230</v>
+      </c>
+      <c r="H50" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" t="s">
+        <v>232</v>
+      </c>
+      <c r="H51" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" t="s">
+        <v>234</v>
+      </c>
+      <c r="H52" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" t="s">
+        <v>236</v>
+      </c>
+      <c r="H53" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="H54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30.75">
+      <c r="A59" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+    </row>
+    <row r="64" spans="1:8" ht="30.75">
+      <c r="A64" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H64" xr:uid="{44886F52-D7D0-4D08-B2D7-D1AD344D9EAF}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H64">
+      <sortCondition ref="H1:H64"/>
+    </sortState>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="G54" r:id="rId1" xr:uid="{BF410496-DCFB-4034-BC8C-E06821CF3C62}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{187EC43D-B458-43E6-ADE2-1BE4FBEBA462}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J65"/>
@@ -4462,22 +5995,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>148</v>
+        <v>243</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>94</v>
@@ -4503,7 +6036,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F2" s="3">
         <v>46197</v>
@@ -4535,13 +6068,13 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H3" t="s">
         <v>102</v>
@@ -4558,7 +6091,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>143</v>
@@ -4582,7 +6115,7 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
         <v>143</v>
@@ -4591,7 +6124,7 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="F5" s="3">
         <v>46244</v>
@@ -4614,7 +6147,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
         <v>143</v>
@@ -4623,7 +6156,7 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F6" s="3">
         <v>46284</v>
@@ -4646,7 +6179,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
         <v>143</v>
@@ -4655,7 +6188,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F7" s="3">
         <v>46284</v>
@@ -4678,7 +6211,7 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
         <v>143</v>
@@ -4702,7 +6235,7 @@
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
         <v>143</v>
@@ -4711,7 +6244,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F9" s="3">
         <v>46283</v>
@@ -4734,7 +6267,7 @@
         <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
         <v>143</v>
@@ -4743,7 +6276,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F10" s="3">
         <v>46286</v>
@@ -4775,13 +6308,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F11" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G11" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H11" t="s">
         <v>102</v>
@@ -4798,7 +6331,7 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
         <v>143</v>
@@ -4807,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F12" s="3">
         <v>46285</v>
@@ -4830,16 +6363,16 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F13" s="3">
         <v>46286</v>
@@ -4862,7 +6395,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
         <v>143</v>
@@ -4871,13 +6404,13 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>251</v>
       </c>
       <c r="F14" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G14" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H14" t="s">
         <v>99</v>
@@ -4894,7 +6427,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C15" t="s">
         <v>143</v>
@@ -4918,7 +6451,7 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
         <v>143</v>
@@ -4927,7 +6460,7 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F16" s="3">
         <v>46283</v>
@@ -4950,7 +6483,7 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
         <v>143</v>
@@ -4959,7 +6492,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F17" s="3">
         <v>46286</v>
@@ -4982,7 +6515,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
         <v>143</v>
@@ -4991,7 +6524,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F18" s="3">
         <v>46283</v>
@@ -5014,7 +6547,7 @@
         <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C19" t="s">
         <v>143</v>
@@ -5023,7 +6556,7 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="F19" s="3">
         <v>46119</v>
@@ -5043,7 +6576,7 @@
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
         <v>143</v>
@@ -5067,7 +6600,7 @@
         <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
         <v>143</v>
@@ -5091,7 +6624,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
         <v>143</v>
@@ -5115,7 +6648,7 @@
         <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s">
         <v>143</v>
@@ -5124,7 +6657,7 @@
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F23" s="3">
         <v>46283</v>
@@ -5156,13 +6689,13 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G24" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H24" t="s">
         <v>102</v>
@@ -5179,7 +6712,7 @@
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
         <v>143</v>
@@ -5188,7 +6721,7 @@
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F25" s="3">
         <v>46284</v>
@@ -5211,16 +6744,16 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F26" s="3">
         <v>46286</v>
@@ -5243,7 +6776,7 @@
         <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C27" t="s">
         <v>143</v>
@@ -5276,13 +6809,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F28" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G28" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H28" t="s">
         <v>102</v>
@@ -5299,7 +6832,7 @@
         <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C29" t="s">
         <v>143</v>
@@ -5323,7 +6856,7 @@
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
         <v>143</v>
@@ -5332,7 +6865,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="F30" s="3">
         <v>46279</v>
@@ -5352,7 +6885,7 @@
         <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s">
         <v>143</v>
@@ -5376,7 +6909,7 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C32" t="s">
         <v>143</v>
@@ -5385,7 +6918,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F32" s="3">
         <v>46285</v>
@@ -5408,7 +6941,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
         <v>143</v>
@@ -5417,7 +6950,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F33" s="3">
         <v>46283</v>
@@ -5440,7 +6973,7 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C34" t="s">
         <v>143</v>
@@ -5449,13 +6982,13 @@
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F34" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G34" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H34" t="s">
         <v>99</v>
@@ -5472,7 +7005,7 @@
         <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C35" t="s">
         <v>143</v>
@@ -5481,13 +7014,13 @@
         <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F35" s="4">
         <v>46010</v>
       </c>
       <c r="G35" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H35" t="s">
         <v>99</v>
@@ -5504,7 +7037,7 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
         <v>143</v>
@@ -5513,7 +7046,7 @@
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F36" s="3">
         <v>46284</v>
@@ -5536,7 +7069,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
         <v>143</v>
@@ -5560,7 +7093,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C38" t="s">
         <v>143</v>
@@ -5584,7 +7117,7 @@
         <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C39" t="s">
         <v>143</v>
@@ -5608,7 +7141,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
         <v>143</v>
@@ -5617,7 +7150,7 @@
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="F40" s="4">
         <v>46265</v>
@@ -5637,7 +7170,7 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
         <v>143</v>
@@ -5646,7 +7179,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F41" s="3">
         <v>46285</v>
@@ -5669,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C42" t="s">
         <v>143</v>
@@ -5693,7 +7226,7 @@
         <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C43" t="s">
         <v>143</v>
@@ -5702,7 +7235,7 @@
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F43" s="3">
         <v>46284</v>
@@ -5725,7 +7258,7 @@
         <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C44" t="s">
         <v>143</v>
@@ -5749,7 +7282,7 @@
         <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C45" t="s">
         <v>143</v>
@@ -5773,16 +7306,16 @@
         <v>79</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F46" s="3">
         <v>46286</v>
@@ -5805,7 +7338,7 @@
         <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C47" t="s">
         <v>143</v>
@@ -5814,7 +7347,7 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F47" s="3">
         <v>46283</v>
@@ -5846,13 +7379,13 @@
         <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F48" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G48" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H48" t="s">
         <v>102</v>
@@ -5869,7 +7402,7 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C49" t="s">
         <v>143</v>
@@ -5893,7 +7426,7 @@
         <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C50" t="s">
         <v>143</v>
@@ -5917,7 +7450,7 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C51" t="s">
         <v>143</v>
@@ -5950,13 +7483,13 @@
         <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F52" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G52" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H52" t="s">
         <v>102</v>
@@ -5973,7 +7506,7 @@
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C53" t="s">
         <v>143</v>
@@ -5997,7 +7530,7 @@
         <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C54" t="s">
         <v>143</v>
@@ -6021,7 +7554,7 @@
         <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C55" t="s">
         <v>143</v>
@@ -6045,7 +7578,7 @@
         <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
         <v>143</v>
@@ -6069,7 +7602,7 @@
         <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C57" t="s">
         <v>143</v>
@@ -6102,13 +7635,13 @@
         <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F58" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G58" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H58" t="s">
         <v>102</v>
@@ -6125,7 +7658,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C59" t="s">
         <v>143</v>
@@ -6134,7 +7667,7 @@
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F59" s="3">
         <v>46286</v>
@@ -6166,13 +7699,13 @@
         <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F60" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="G60" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="H60" t="s">
         <v>102</v>
@@ -6189,7 +7722,7 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
         <v>143</v>
@@ -6198,7 +7731,7 @@
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F61" s="3">
         <v>46286</v>
@@ -6221,7 +7754,7 @@
         <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C62" t="s">
         <v>143</v>
@@ -6230,7 +7763,7 @@
         <v>7</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="F62" s="3">
         <v>46286</v>
@@ -6253,7 +7786,7 @@
         <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C63" t="s">
         <v>143</v>
@@ -6277,7 +7810,7 @@
         <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C64" t="s">
         <v>143</v>
@@ -6301,7 +7834,7 @@
         <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C65" t="s">
         <v>143</v>
@@ -6335,7 +7868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E020160-1EC6-4376-AD82-CC2F813550D2}">
   <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
@@ -6358,28 +7891,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>148</v>
+        <v>243</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>94</v>
@@ -6440,10 +7973,10 @@
         <v>143</v>
       </c>
       <c r="H3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J3" t="s">
         <v>102</v>
@@ -6472,10 +8005,10 @@
         <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I4" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J4" t="s">
         <v>102</v>
@@ -6492,7 +8025,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
         <v>143</v>
@@ -6504,10 +8037,10 @@
         <v>143</v>
       </c>
       <c r="H5" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I5" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J5" t="s">
         <v>99</v>
@@ -6524,7 +8057,7 @@
         <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
         <v>143</v>
@@ -6533,13 +8066,13 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="F6" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="G6" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H6" s="3">
         <v>46287</v>
@@ -6562,7 +8095,7 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
         <v>143</v>
@@ -6571,13 +8104,13 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="G7" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H7" s="3">
         <v>46287</v>
@@ -6600,7 +8133,7 @@
         <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
         <v>143</v>
@@ -6609,10 +8142,10 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F8" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="I8"/>
       <c r="J8" t="s">
@@ -6630,7 +8163,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
         <v>143</v>
@@ -6639,13 +8172,13 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F9" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="G9" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="H9" s="3">
         <v>46244</v>
@@ -6668,7 +8201,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
         <v>143</v>
@@ -6677,13 +8210,13 @@
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F10" t="s">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="G10" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H10" s="3">
         <v>46287</v>
@@ -6706,7 +8239,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
         <v>143</v>
@@ -6715,13 +8248,13 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="F11" t="s">
-        <v>171</v>
+        <v>259</v>
       </c>
       <c r="G11" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H11" s="3">
         <v>46287</v>
@@ -6744,7 +8277,7 @@
         <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C12" t="s">
         <v>143</v>
@@ -6753,10 +8286,10 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="s">
@@ -6774,7 +8307,7 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
         <v>143</v>
@@ -6783,13 +8316,13 @@
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F13" t="s">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H13" s="3">
         <v>46286</v>
@@ -6812,7 +8345,7 @@
         <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
         <v>143</v>
@@ -6821,13 +8354,13 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="G14" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H14" s="3">
         <v>46287</v>
@@ -6850,7 +8383,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
         <v>143</v>
@@ -6859,13 +8392,13 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>263</v>
       </c>
       <c r="G15" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H15" s="3">
         <v>46287</v>
@@ -6888,7 +8421,7 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
         <v>143</v>
@@ -6897,13 +8430,13 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F16" t="s">
-        <v>181</v>
+        <v>264</v>
       </c>
       <c r="G16" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H16" s="3">
         <v>46287</v>
@@ -6926,7 +8459,7 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
         <v>143</v>
@@ -6935,13 +8468,13 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="G17" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H17" s="3">
         <v>46287</v>
@@ -6959,24 +8492,24 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
       <c r="G18" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H18" s="3">
         <v>46287</v>
@@ -6999,7 +8532,7 @@
         <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C19" t="s">
         <v>143</v>
@@ -7008,13 +8541,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="F19" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
       <c r="G19" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="H19" s="3">
         <v>46119</v>
@@ -7034,7 +8567,7 @@
         <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
         <v>143</v>
@@ -7043,10 +8576,10 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F20" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="I20"/>
       <c r="J20" t="s">
@@ -7064,7 +8597,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
         <v>143</v>
@@ -7073,7 +8606,7 @@
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="F21" t="s">
         <v>143</v>
@@ -7094,22 +8627,22 @@
         <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F22" t="s">
-        <v>192</v>
+        <v>269</v>
       </c>
       <c r="G22" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H22" s="3">
         <v>46287</v>
@@ -7132,22 +8665,22 @@
         <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F23" t="s">
-        <v>194</v>
+        <v>270</v>
       </c>
       <c r="G23" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H23" s="3">
         <v>46287</v>
@@ -7170,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C24" t="s">
         <v>143</v>
@@ -7179,13 +8712,13 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F24" t="s">
-        <v>196</v>
+        <v>271</v>
       </c>
       <c r="G24" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H24" s="3">
         <v>46287</v>
@@ -7208,7 +8741,7 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C25" t="s">
         <v>143</v>
@@ -7217,10 +8750,10 @@
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F25" t="s">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="I25"/>
       <c r="J25" t="s">
@@ -7238,7 +8771,7 @@
         <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C26" t="s">
         <v>143</v>
@@ -7247,10 +8780,10 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F26" t="s">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="I26"/>
       <c r="J26" t="s">
@@ -7268,7 +8801,7 @@
         <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C27" t="s">
         <v>143</v>
@@ -7277,10 +8810,10 @@
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F27" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="H27" s="3">
         <v>46279</v>
@@ -7300,7 +8833,7 @@
         <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
         <v>143</v>
@@ -7309,10 +8842,10 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F28" t="s">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="s">
@@ -7330,7 +8863,7 @@
         <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C29" t="s">
         <v>143</v>
@@ -7339,10 +8872,10 @@
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F29" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="I29"/>
       <c r="J29" t="s">
@@ -7360,7 +8893,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
         <v>143</v>
@@ -7369,16 +8902,16 @@
         <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="H30" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I30" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J30" t="s">
         <v>99</v>
@@ -7395,7 +8928,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s">
         <v>143</v>
@@ -7404,10 +8937,10 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="I31"/>
       <c r="J31" t="s">
@@ -7425,7 +8958,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C32" t="s">
         <v>143</v>
@@ -7434,19 +8967,19 @@
         <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>211</v>
+        <v>147</v>
       </c>
       <c r="F32" t="s">
         <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="H32" s="4">
         <v>46010</v>
       </c>
       <c r="I32" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J32" t="s">
         <v>99</v>
@@ -7463,7 +8996,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
         <v>143</v>
@@ -7472,13 +9005,13 @@
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>212</v>
+        <v>148</v>
       </c>
       <c r="F33" t="s">
         <v>143</v>
       </c>
       <c r="G33" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H33" s="3">
         <v>46287</v>
@@ -7501,7 +9034,7 @@
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C34" t="s">
         <v>143</v>
@@ -7510,10 +9043,10 @@
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>214</v>
+        <v>279</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="s">
@@ -7531,7 +9064,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C35" t="s">
         <v>143</v>
@@ -7540,13 +9073,13 @@
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="F35" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H35" s="3">
         <v>46287</v>
@@ -7569,7 +9102,7 @@
         <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
         <v>143</v>
@@ -7578,13 +9111,13 @@
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="G36" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H36" s="3">
         <v>46287</v>
@@ -7607,7 +9140,7 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
         <v>143</v>
@@ -7616,10 +9149,10 @@
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F37" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="I37"/>
       <c r="J37" t="s">
@@ -7637,7 +9170,7 @@
         <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C38" t="s">
         <v>143</v>
@@ -7646,10 +9179,10 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="F38" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="s">
@@ -7667,7 +9200,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s">
         <v>143</v>
@@ -7676,13 +9209,13 @@
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F39" t="s">
-        <v>224</v>
+        <v>284</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="H39" s="4">
         <v>46265</v>
@@ -7702,7 +9235,7 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C40" t="s">
         <v>143</v>
@@ -7711,10 +9244,10 @@
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F40" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="I40"/>
       <c r="J40" t="s">
@@ -7732,7 +9265,7 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
         <v>143</v>
@@ -7741,13 +9274,13 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F41" t="s">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="G41" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H41" s="3">
         <v>46287</v>
@@ -7770,7 +9303,7 @@
         <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C42" t="s">
         <v>143</v>
@@ -7779,10 +9312,10 @@
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F42" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="I42"/>
       <c r="J42" t="s">
@@ -7800,7 +9333,7 @@
         <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C43" t="s">
         <v>143</v>
@@ -7809,13 +9342,13 @@
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F43" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H43" s="3">
         <v>46287</v>
@@ -7838,7 +9371,7 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C44" t="s">
         <v>143</v>
@@ -7847,10 +9380,10 @@
         <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F44" t="s">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="I44"/>
       <c r="J44" t="s">
@@ -7868,7 +9401,7 @@
         <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C45" t="s">
         <v>143</v>
@@ -7877,10 +9410,10 @@
         <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F45" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="I45"/>
       <c r="J45" t="s">
@@ -7898,7 +9431,7 @@
         <v>82</v>
       </c>
       <c r="B46" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C46" t="s">
         <v>143</v>
@@ -7907,10 +9440,10 @@
         <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="I46"/>
       <c r="J46" t="s">
@@ -7928,7 +9461,7 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C47" t="s">
         <v>143</v>
@@ -7937,7 +9470,7 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>239</v>
+        <v>149</v>
       </c>
       <c r="F47" t="s">
         <v>143</v>
@@ -7958,16 +9491,16 @@
         <v>83</v>
       </c>
       <c r="B48" t="s">
+        <v>246</v>
+      </c>
+      <c r="C48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" t="s">
         <v>150</v>
-      </c>
-      <c r="C48" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" t="s">
-        <v>240</v>
       </c>
       <c r="F48" t="s">
         <v>143</v>
@@ -7988,7 +9521,7 @@
         <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C49" t="s">
         <v>143</v>
@@ -7997,10 +9530,10 @@
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="F49" t="s">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="I49"/>
       <c r="J49" t="s">
@@ -8027,16 +9560,16 @@
         <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="F50" t="s">
         <v>143</v>
       </c>
       <c r="H50" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I50" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J50" t="s">
         <v>102</v>
@@ -8053,7 +9586,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C51" t="s">
         <v>143</v>
@@ -8062,13 +9595,13 @@
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="F51" t="s">
         <v>143</v>
       </c>
       <c r="G51" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H51" s="3">
         <v>46287</v>
@@ -8091,7 +9624,7 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C52" t="s">
         <v>143</v>
@@ -8100,13 +9633,13 @@
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="F52" t="s">
         <v>143</v>
       </c>
       <c r="G52" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H52" s="3">
         <v>46287</v>
@@ -8129,7 +9662,7 @@
         <v>34</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C53" t="s">
         <v>143</v>
@@ -8138,7 +9671,7 @@
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s">
         <v>143</v>
@@ -8165,7 +9698,7 @@
         <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C54" t="s">
         <v>143</v>
@@ -8174,10 +9707,10 @@
         <v>7</v>
       </c>
       <c r="E54" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F54" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="I54"/>
       <c r="J54" t="s">
@@ -8195,7 +9728,7 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C55" t="s">
         <v>143</v>
@@ -8204,10 +9737,10 @@
         <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="F55" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="I55"/>
       <c r="J55" t="s">
@@ -8225,7 +9758,7 @@
         <v>87</v>
       </c>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C56" t="s">
         <v>143</v>
@@ -8234,10 +9767,10 @@
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="F56" t="s">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="I56"/>
       <c r="J56" t="s">
@@ -8255,7 +9788,7 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C57" t="s">
         <v>143</v>
@@ -8264,13 +9797,13 @@
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>253</v>
+        <v>155</v>
       </c>
       <c r="F57" t="s">
         <v>143</v>
       </c>
       <c r="G57" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="H57" s="3">
         <v>46287</v>
@@ -8293,7 +9826,7 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C58" t="s">
         <v>143</v>
@@ -8332,10 +9865,10 @@
         <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I59" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J59" t="s">
         <v>102</v>
@@ -8361,10 +9894,10 @@
         <v>19</v>
       </c>
       <c r="H60" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I60" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J60" t="s">
         <v>102</v>
@@ -8390,10 +9923,10 @@
         <v>19</v>
       </c>
       <c r="H61" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I61" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J61" t="s">
         <v>102</v>
@@ -8419,10 +9952,10 @@
         <v>19</v>
       </c>
       <c r="H62" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I62" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J62" t="s">
         <v>102</v>
@@ -8439,7 +9972,7 @@
         <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C63" t="s">
         <v>143</v>
@@ -8463,7 +9996,7 @@
         <v>43</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C64" t="s">
         <v>143</v>
@@ -8496,10 +10029,10 @@
         <v>19</v>
       </c>
       <c r="H65" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="I65" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="J65" t="s">
         <v>102</v>
@@ -8521,7 +10054,2126 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442FBDF7-950F-490D-8BB5-6507E5181B2E}">
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="88" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" s="3">
+        <v>46197</v>
+      </c>
+      <c r="I2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4" t="s">
+        <v>245</v>
+      </c>
+      <c r="J4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="J6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" t="s">
+        <v>255</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="J7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" t="s">
+        <v>256</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46244</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="J9" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G10" t="s">
+        <v>258</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="J10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" t="s">
+        <v>259</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="J11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>162</v>
+      </c>
+      <c r="G13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46286</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="J13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.65625</v>
+      </c>
+      <c r="J14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>249</v>
+      </c>
+      <c r="F15" t="s">
+        <v>166</v>
+      </c>
+      <c r="G15" t="s">
+        <v>263</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46288</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="J16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" t="s">
+        <v>265</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46288</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" t="s">
+        <v>266</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J18" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" t="s">
+        <v>267</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46119</v>
+      </c>
+      <c r="J19" t="s">
+        <v>99</v>
+      </c>
+      <c r="K19" t="s">
+        <v>102</v>
+      </c>
+      <c r="L19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" t="s">
+        <v>268</v>
+      </c>
+      <c r="I20"/>
+      <c r="J20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" t="s">
+        <v>143</v>
+      </c>
+      <c r="I21"/>
+      <c r="J21" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" t="s">
+        <v>102</v>
+      </c>
+      <c r="L21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" t="s">
+        <v>241</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>180</v>
+      </c>
+      <c r="G22" t="s">
+        <v>269</v>
+      </c>
+      <c r="H22" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J22" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" t="s">
+        <v>102</v>
+      </c>
+      <c r="L22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C23" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>182</v>
+      </c>
+      <c r="G23" t="s">
+        <v>270</v>
+      </c>
+      <c r="H23" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J23" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C24" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" t="s">
+        <v>271</v>
+      </c>
+      <c r="H24" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I24" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J24" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" t="s">
+        <v>102</v>
+      </c>
+      <c r="L24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>186</v>
+      </c>
+      <c r="G25" t="s">
+        <v>272</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>102</v>
+      </c>
+      <c r="L25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>188</v>
+      </c>
+      <c r="G26" t="s">
+        <v>273</v>
+      </c>
+      <c r="I26"/>
+      <c r="J26" t="s">
+        <v>102</v>
+      </c>
+      <c r="K26" t="s">
+        <v>99</v>
+      </c>
+      <c r="L26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" t="s">
+        <v>274</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46279</v>
+      </c>
+      <c r="J27" t="s">
+        <v>99</v>
+      </c>
+      <c r="K27" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>252</v>
+      </c>
+      <c r="C28" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" t="s">
+        <v>275</v>
+      </c>
+      <c r="I28"/>
+      <c r="J28" t="s">
+        <v>102</v>
+      </c>
+      <c r="K28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s">
+        <v>246</v>
+      </c>
+      <c r="C29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>194</v>
+      </c>
+      <c r="G29" t="s">
+        <v>276</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29" t="s">
+        <v>102</v>
+      </c>
+      <c r="K29" t="s">
+        <v>99</v>
+      </c>
+      <c r="L29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" t="s">
+        <v>277</v>
+      </c>
+      <c r="H30" t="s">
+        <v>245</v>
+      </c>
+      <c r="I30" t="s">
+        <v>245</v>
+      </c>
+      <c r="J30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K30" t="s">
+        <v>102</v>
+      </c>
+      <c r="L30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>208</v>
+      </c>
+      <c r="G31" t="s">
+        <v>278</v>
+      </c>
+      <c r="I31"/>
+      <c r="J31" t="s">
+        <v>102</v>
+      </c>
+      <c r="K31" t="s">
+        <v>99</v>
+      </c>
+      <c r="L31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>247</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" t="s">
+        <v>143</v>
+      </c>
+      <c r="H32" s="4">
+        <v>46010</v>
+      </c>
+      <c r="I32" t="s">
+        <v>245</v>
+      </c>
+      <c r="J32" t="s">
+        <v>99</v>
+      </c>
+      <c r="K32" t="s">
+        <v>102</v>
+      </c>
+      <c r="L32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>148</v>
+      </c>
+      <c r="G33" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="3">
+        <v>46288</v>
+      </c>
+      <c r="I33" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="J33" t="s">
+        <v>99</v>
+      </c>
+      <c r="K33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>252</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" t="s">
+        <v>279</v>
+      </c>
+      <c r="I34"/>
+      <c r="J34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K34" t="s">
+        <v>102</v>
+      </c>
+      <c r="L34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>168</v>
+      </c>
+      <c r="G35" t="s">
+        <v>280</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I35" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="J35" t="s">
+        <v>99</v>
+      </c>
+      <c r="K35" t="s">
+        <v>102</v>
+      </c>
+      <c r="L35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>222</v>
+      </c>
+      <c r="G36" t="s">
+        <v>281</v>
+      </c>
+      <c r="H36" s="3">
+        <v>46288</v>
+      </c>
+      <c r="I36" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="J36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K36" t="s">
+        <v>102</v>
+      </c>
+      <c r="L36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>210</v>
+      </c>
+      <c r="G37" t="s">
+        <v>282</v>
+      </c>
+      <c r="I37"/>
+      <c r="J37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K37" t="s">
+        <v>99</v>
+      </c>
+      <c r="L37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" t="s">
+        <v>252</v>
+      </c>
+      <c r="C38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>212</v>
+      </c>
+      <c r="G38" t="s">
+        <v>283</v>
+      </c>
+      <c r="I38"/>
+      <c r="J38" t="s">
+        <v>102</v>
+      </c>
+      <c r="K38" t="s">
+        <v>102</v>
+      </c>
+      <c r="L38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" t="s">
+        <v>284</v>
+      </c>
+      <c r="H39" s="4">
+        <v>46265</v>
+      </c>
+      <c r="J39" t="s">
+        <v>99</v>
+      </c>
+      <c r="K39" t="s">
+        <v>102</v>
+      </c>
+      <c r="L39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>216</v>
+      </c>
+      <c r="G40" t="s">
+        <v>285</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40" t="s">
+        <v>102</v>
+      </c>
+      <c r="K40" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" t="s">
+        <v>218</v>
+      </c>
+      <c r="G41" t="s">
+        <v>286</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46288</v>
+      </c>
+      <c r="I41" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J41" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41" t="s">
+        <v>102</v>
+      </c>
+      <c r="L41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
+        <v>246</v>
+      </c>
+      <c r="C42" t="s">
+        <v>143</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>220</v>
+      </c>
+      <c r="G42" t="s">
+        <v>287</v>
+      </c>
+      <c r="I42"/>
+      <c r="J42" t="s">
+        <v>102</v>
+      </c>
+      <c r="K42" t="s">
+        <v>99</v>
+      </c>
+      <c r="L42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>224</v>
+      </c>
+      <c r="G43" t="s">
+        <v>288</v>
+      </c>
+      <c r="H43" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J43" t="s">
+        <v>99</v>
+      </c>
+      <c r="K43" t="s">
+        <v>102</v>
+      </c>
+      <c r="L43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>226</v>
+      </c>
+      <c r="G44" t="s">
+        <v>289</v>
+      </c>
+      <c r="I44"/>
+      <c r="J44" t="s">
+        <v>102</v>
+      </c>
+      <c r="K44" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" t="s">
+        <v>246</v>
+      </c>
+      <c r="C45" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" t="s">
+        <v>290</v>
+      </c>
+      <c r="I45"/>
+      <c r="J45" t="s">
+        <v>102</v>
+      </c>
+      <c r="K45" t="s">
+        <v>99</v>
+      </c>
+      <c r="L45" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" t="s">
+        <v>252</v>
+      </c>
+      <c r="C46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>230</v>
+      </c>
+      <c r="G46" t="s">
+        <v>291</v>
+      </c>
+      <c r="I46"/>
+      <c r="J46" t="s">
+        <v>102</v>
+      </c>
+      <c r="K46" t="s">
+        <v>102</v>
+      </c>
+      <c r="L46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" t="s">
+        <v>143</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" t="s">
+        <v>143</v>
+      </c>
+      <c r="I47"/>
+      <c r="J47" t="s">
+        <v>102</v>
+      </c>
+      <c r="K47" t="s">
+        <v>102</v>
+      </c>
+      <c r="L47" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" t="s">
+        <v>246</v>
+      </c>
+      <c r="C48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" t="s">
+        <v>143</v>
+      </c>
+      <c r="I48"/>
+      <c r="J48" t="s">
+        <v>102</v>
+      </c>
+      <c r="K48" t="s">
+        <v>99</v>
+      </c>
+      <c r="L48" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" t="s">
+        <v>252</v>
+      </c>
+      <c r="C49" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" t="s">
+        <v>292</v>
+      </c>
+      <c r="I49"/>
+      <c r="J49" t="s">
+        <v>102</v>
+      </c>
+      <c r="K49" t="s">
+        <v>102</v>
+      </c>
+      <c r="L49" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>151</v>
+      </c>
+      <c r="G50" t="s">
+        <v>143</v>
+      </c>
+      <c r="H50" t="s">
+        <v>245</v>
+      </c>
+      <c r="I50" t="s">
+        <v>245</v>
+      </c>
+      <c r="J50" t="s">
+        <v>102</v>
+      </c>
+      <c r="K50" t="s">
+        <v>102</v>
+      </c>
+      <c r="L50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>152</v>
+      </c>
+      <c r="G51" t="s">
+        <v>143</v>
+      </c>
+      <c r="H51" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I51" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J51" t="s">
+        <v>99</v>
+      </c>
+      <c r="K51" t="s">
+        <v>102</v>
+      </c>
+      <c r="L51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>153</v>
+      </c>
+      <c r="G52" t="s">
+        <v>143</v>
+      </c>
+      <c r="H52" s="3">
+        <v>46288</v>
+      </c>
+      <c r="I52" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J52" t="s">
+        <v>99</v>
+      </c>
+      <c r="K52" t="s">
+        <v>102</v>
+      </c>
+      <c r="L52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" t="s">
+        <v>154</v>
+      </c>
+      <c r="G53" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="3">
+        <v>46286</v>
+      </c>
+      <c r="I53" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J53" t="s">
+        <v>99</v>
+      </c>
+      <c r="K53" t="s">
+        <v>102</v>
+      </c>
+      <c r="L53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" t="s">
+        <v>252</v>
+      </c>
+      <c r="C54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>234</v>
+      </c>
+      <c r="G54" t="s">
+        <v>293</v>
+      </c>
+      <c r="I54"/>
+      <c r="J54" t="s">
+        <v>102</v>
+      </c>
+      <c r="K54" t="s">
+        <v>102</v>
+      </c>
+      <c r="L54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
+        <v>246</v>
+      </c>
+      <c r="C55" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>236</v>
+      </c>
+      <c r="G55" t="s">
+        <v>294</v>
+      </c>
+      <c r="I55"/>
+      <c r="J55" t="s">
+        <v>102</v>
+      </c>
+      <c r="K55" t="s">
+        <v>99</v>
+      </c>
+      <c r="L55" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C56" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" t="s">
+        <v>238</v>
+      </c>
+      <c r="G56" t="s">
+        <v>295</v>
+      </c>
+      <c r="I56"/>
+      <c r="J56" t="s">
+        <v>102</v>
+      </c>
+      <c r="K56" t="s">
+        <v>102</v>
+      </c>
+      <c r="L56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>247</v>
+      </c>
+      <c r="C57" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>155</v>
+      </c>
+      <c r="G57" t="s">
+        <v>143</v>
+      </c>
+      <c r="H57" s="3">
+        <v>46287</v>
+      </c>
+      <c r="I57" s="5">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J57" t="s">
+        <v>99</v>
+      </c>
+      <c r="K57" t="s">
+        <v>102</v>
+      </c>
+      <c r="L57" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" t="s">
+        <v>246</v>
+      </c>
+      <c r="C58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>143</v>
+      </c>
+      <c r="G58" t="s">
+        <v>143</v>
+      </c>
+      <c r="I58"/>
+      <c r="J58" t="s">
+        <v>102</v>
+      </c>
+      <c r="K58" t="s">
+        <v>99</v>
+      </c>
+      <c r="L58" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>245</v>
+      </c>
+      <c r="I59" t="s">
+        <v>245</v>
+      </c>
+      <c r="J59" t="s">
+        <v>102</v>
+      </c>
+      <c r="K59" t="s">
+        <v>102</v>
+      </c>
+      <c r="L59" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>245</v>
+      </c>
+      <c r="I60" t="s">
+        <v>245</v>
+      </c>
+      <c r="J60" t="s">
+        <v>102</v>
+      </c>
+      <c r="K60" t="s">
+        <v>102</v>
+      </c>
+      <c r="L60" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>245</v>
+      </c>
+      <c r="I61" t="s">
+        <v>245</v>
+      </c>
+      <c r="J61" t="s">
+        <v>102</v>
+      </c>
+      <c r="K61" t="s">
+        <v>102</v>
+      </c>
+      <c r="L61" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>245</v>
+      </c>
+      <c r="I62" t="s">
+        <v>245</v>
+      </c>
+      <c r="J62" t="s">
+        <v>102</v>
+      </c>
+      <c r="K62" t="s">
+        <v>102</v>
+      </c>
+      <c r="L62" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" t="s">
+        <v>252</v>
+      </c>
+      <c r="C63" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="I63"/>
+      <c r="J63" t="s">
+        <v>102</v>
+      </c>
+      <c r="K63" t="s">
+        <v>102</v>
+      </c>
+      <c r="L63" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" t="s">
+        <v>252</v>
+      </c>
+      <c r="C64" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+      <c r="I64"/>
+      <c r="J64" t="s">
+        <v>102</v>
+      </c>
+      <c r="K64" t="s">
+        <v>102</v>
+      </c>
+      <c r="L64" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" t="s">
+        <v>143</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>245</v>
+      </c>
+      <c r="I65" t="s">
+        <v>245</v>
+      </c>
+      <c r="J65" t="s">
+        <v>102</v>
+      </c>
+      <c r="K65" t="s">
+        <v>102</v>
+      </c>
+      <c r="L65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L65" xr:uid="{187EC43D-B458-43E6-ADE2-1BE4FBEBA462}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L65">
+      <sortCondition ref="F1:F65"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB763E34-5FF3-4B63-834F-6A8A56534A77}">
   <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
@@ -8536,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="C1" s="3">
         <v>46286</v>
@@ -8577,7 +12229,7 @@
         <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -8588,7 +12240,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -8596,7 +12248,7 @@
         <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -8604,10 +12256,10 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -8615,10 +12267,10 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -8626,10 +12278,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -8637,7 +12289,7 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -8645,10 +12297,10 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -8656,10 +12308,10 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -8670,7 +12322,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -8678,10 +12330,10 @@
         <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -8689,10 +12341,10 @@
         <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -8700,10 +12352,10 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -8711,7 +12363,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -8719,10 +12371,10 @@
         <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8730,10 +12382,10 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -8741,10 +12393,10 @@
         <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8752,10 +12404,10 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -8763,7 +12415,7 @@
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -8771,7 +12423,7 @@
         <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -8779,7 +12431,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8787,10 +12439,10 @@
         <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -8801,7 +12453,7 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -8809,10 +12461,10 @@
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -8820,10 +12472,10 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8831,7 +12483,7 @@
         <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -8842,7 +12494,7 @@
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -8850,7 +12502,7 @@
         <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8858,10 +12510,10 @@
         <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8869,7 +12521,7 @@
         <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8877,10 +12529,10 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -8888,10 +12540,10 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -8899,10 +12551,10 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8910,10 +12562,10 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -8921,10 +12573,10 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -8932,7 +12584,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -8940,7 +12592,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -8948,7 +12600,7 @@
         <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -8956,10 +12608,10 @@
         <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -8967,10 +12619,10 @@
         <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -8978,7 +12630,7 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -8986,10 +12638,10 @@
         <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -8997,7 +12649,7 @@
         <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -9005,7 +12657,7 @@
         <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9013,10 +12665,10 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9024,10 +12676,10 @@
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9038,7 +12690,7 @@
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9046,7 +12698,7 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9054,7 +12706,7 @@
         <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -9062,7 +12714,7 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -9073,7 +12725,7 @@
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -9081,7 +12733,7 @@
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -9089,7 +12741,7 @@
         <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -9097,7 +12749,7 @@
         <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -9105,7 +12757,7 @@
         <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -9113,7 +12765,7 @@
         <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -9124,7 +12776,7 @@
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -9132,10 +12784,10 @@
         <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -9146,7 +12798,7 @@
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -9154,10 +12806,10 @@
         <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -9165,10 +12817,10 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -9176,7 +12828,7 @@
         <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9184,7 +12836,7 @@
         <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9192,7 +12844,7 @@
         <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/AcompanhamentoFaturados.xlsx
+++ b/AcompanhamentoFaturados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PedroMencariniGarcia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D3C2102-7B3E-4FF4-81B2-F9F96532F31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97522E6A-FAC3-4249-A317-E9A43BD3EEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Contatos!$A$1:$F$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mesclado!$A$1:$H$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'23_09'!$A$1:$L$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Monitor!$A:$I</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Monitor!$A:$H</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3318" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="297">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -4611,57 +4611,54 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44886F52-D7D0-4D08-B2D7-D1AD344D9EAF}">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="88" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="88" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
+      <c r="C1" s="9" t="s">
+        <v>1</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>145</v>
       </c>
+      <c r="I1" s="12" t="s">
+        <v>146</v>
+      </c>
       <c r="J1" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="K1" s="12" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4669,27 +4666,24 @@
         <v>143</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F2" s="10"/>
       <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="J2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="H2" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="I2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4697,27 +4691,24 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F3" s="10"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="18" t="s">
+      <c r="H3" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="J3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="I3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -4725,27 +4716,24 @@
         <v>11</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="F4" s="10"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="J4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="I4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -4753,27 +4741,24 @@
         <v>149</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F5" s="10"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="18" t="s">
+      <c r="H5" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="J5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="I5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4781,27 +4766,24 @@
         <v>150</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F6" s="10"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="I6" t="s">
+        <v>143</v>
+      </c>
       <c r="J6" t="s">
         <v>143</v>
       </c>
-      <c r="K6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -4809,30 +4791,27 @@
         <v>149</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F7" s="10"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="19">
+      <c r="H7" s="19">
         <v>0.91666666666666663</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="I7" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="K7" t="s">
+      <c r="J7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -4840,30 +4819,27 @@
         <v>149</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F8" s="10"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="19">
+      <c r="H8" s="19">
         <v>0.9375</v>
       </c>
+      <c r="I8" t="s">
+        <v>153</v>
+      </c>
       <c r="J8" t="s">
-        <v>153</v>
-      </c>
-      <c r="K8" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4871,27 +4847,24 @@
         <v>150</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F9" s="10"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="I9" t="s">
+        <v>155</v>
+      </c>
       <c r="J9" t="s">
-        <v>155</v>
-      </c>
-      <c r="K9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4899,30 +4872,27 @@
         <v>149</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="19">
+      <c r="H10" s="19">
         <v>0.14583333333333334</v>
       </c>
+      <c r="I10" t="s">
+        <v>157</v>
+      </c>
       <c r="J10" t="s">
-        <v>157</v>
-      </c>
-      <c r="K10" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4930,30 +4900,27 @@
         <v>149</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F11" s="10"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="19">
+      <c r="H11" s="19">
         <v>0.625</v>
       </c>
+      <c r="I11" t="s">
+        <v>159</v>
+      </c>
       <c r="J11" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4961,30 +4928,27 @@
         <v>149</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="19">
+      <c r="H12" s="19">
         <v>0.625</v>
       </c>
+      <c r="I12" t="s">
+        <v>161</v>
+      </c>
       <c r="J12" t="s">
-        <v>161</v>
-      </c>
-      <c r="K12" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4992,27 +4956,24 @@
         <v>150</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F13" s="10"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="I13" t="s">
+        <v>163</v>
+      </c>
       <c r="J13" t="s">
-        <v>163</v>
-      </c>
-      <c r="K13" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -5020,30 +4981,27 @@
         <v>149</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F14" s="10"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="19">
+      <c r="H14" s="19">
         <v>0.625</v>
       </c>
+      <c r="I14" t="s">
+        <v>165</v>
+      </c>
       <c r="J14" t="s">
-        <v>165</v>
-      </c>
-      <c r="K14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -5051,30 +5009,27 @@
         <v>149</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F15" s="10"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="19">
+      <c r="H15" s="19">
         <v>0.65625</v>
       </c>
+      <c r="I15" t="s">
+        <v>167</v>
+      </c>
       <c r="J15" t="s">
-        <v>167</v>
-      </c>
-      <c r="K15" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -5082,30 +5037,27 @@
         <v>149</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="F16" s="10"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="19">
+      <c r="H16" s="19">
         <v>0.25</v>
       </c>
+      <c r="I16" t="s">
+        <v>169</v>
+      </c>
       <c r="J16" t="s">
-        <v>169</v>
-      </c>
-      <c r="K16" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -5113,30 +5065,27 @@
         <v>149</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="F17" s="10"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="19">
+      <c r="H17" s="19">
         <v>0.91666666666666663</v>
       </c>
+      <c r="I17" t="s">
+        <v>171</v>
+      </c>
       <c r="J17" t="s">
-        <v>171</v>
-      </c>
-      <c r="K17" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -5144,30 +5093,27 @@
         <v>149</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F18" s="10"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="19">
+      <c r="H18" s="19">
         <v>0.33333333333333331</v>
       </c>
+      <c r="I18" t="s">
+        <v>173</v>
+      </c>
       <c r="J18" t="s">
-        <v>173</v>
-      </c>
-      <c r="K18" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -5175,30 +5121,27 @@
         <v>149</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F19" s="10"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="19">
+      <c r="H19" s="19">
         <v>0.66666666666666663</v>
       </c>
+      <c r="I19" t="s">
+        <v>175</v>
+      </c>
       <c r="J19" t="s">
-        <v>175</v>
-      </c>
-      <c r="K19" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -5206,28 +5149,25 @@
         <v>149</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F20" s="10"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" t="s">
+        <v>177</v>
+      </c>
       <c r="J20" t="s">
-        <v>177</v>
-      </c>
-      <c r="K20" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -5235,27 +5175,24 @@
         <v>179</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>39</v>
       </c>
+      <c r="F21" s="10"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+      <c r="I21" t="s">
+        <v>180</v>
+      </c>
       <c r="J21" t="s">
-        <v>180</v>
-      </c>
-      <c r="K21" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -5263,27 +5200,24 @@
         <v>179</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F22" s="10"/>
       <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="I22" t="s">
+        <v>182</v>
+      </c>
       <c r="J22" t="s">
-        <v>182</v>
-      </c>
-      <c r="K22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -5291,26 +5225,23 @@
         <v>149</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>7</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="19">
+      <c r="H23" s="19">
         <v>0.54166666666666663</v>
       </c>
+      <c r="I23" t="s">
+        <v>183</v>
+      </c>
       <c r="J23" t="s">
-        <v>183</v>
-      </c>
-      <c r="K23" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -5318,30 +5249,27 @@
         <v>149</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F24" s="10"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="19">
+      <c r="H24" s="19">
         <v>0.64583333333333337</v>
       </c>
+      <c r="I24" t="s">
+        <v>185</v>
+      </c>
       <c r="J24" t="s">
-        <v>185</v>
-      </c>
-      <c r="K24" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -5349,30 +5277,27 @@
         <v>149</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F25" s="10"/>
       <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="20">
+      <c r="H25" s="20">
         <v>0.58333333333333337</v>
       </c>
+      <c r="I25" t="s">
+        <v>187</v>
+      </c>
       <c r="J25" t="s">
-        <v>187</v>
-      </c>
-      <c r="K25" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -5380,27 +5305,24 @@
         <v>179</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F26" s="10"/>
       <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="I26" t="s">
+        <v>189</v>
+      </c>
       <c r="J26" t="s">
-        <v>189</v>
-      </c>
-      <c r="K26" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -5408,27 +5330,24 @@
         <v>150</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="E27" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="I27" t="s">
+        <v>191</v>
+      </c>
       <c r="J27" t="s">
-        <v>191</v>
-      </c>
-      <c r="K27" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -5436,28 +5355,25 @@
         <v>149</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="F28" s="10"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" t="s">
+        <v>193</v>
+      </c>
       <c r="J28" t="s">
-        <v>193</v>
-      </c>
-      <c r="K28" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -5465,27 +5381,24 @@
         <v>179</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="I29" t="s">
+        <v>195</v>
+      </c>
       <c r="J29" t="s">
-        <v>195</v>
-      </c>
-      <c r="K29" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -5493,23 +5406,20 @@
         <v>150</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>7</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="I30" t="s">
+        <v>197</v>
+      </c>
       <c r="J30" t="s">
-        <v>197</v>
-      </c>
-      <c r="K30" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -5517,26 +5427,23 @@
         <v>149</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>7</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="18" t="s">
+      <c r="H31" s="18" t="s">
         <v>148</v>
       </c>
+      <c r="I31" t="s">
+        <v>199</v>
+      </c>
       <c r="J31" t="s">
-        <v>199</v>
-      </c>
-      <c r="K31" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>58</v>
       </c>
@@ -5544,27 +5451,24 @@
         <v>150</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="F32" s="10"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="I32" t="s">
+        <v>201</v>
+      </c>
       <c r="J32" t="s">
-        <v>201</v>
-      </c>
-      <c r="K32" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -5572,30 +5476,27 @@
         <v>149</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F33" s="10"/>
       <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="18" t="s">
+      <c r="H33" s="18" t="s">
         <v>148</v>
       </c>
+      <c r="I33" t="s">
+        <v>203</v>
+      </c>
       <c r="J33" t="s">
-        <v>203</v>
-      </c>
-      <c r="K33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -5603,30 +5504,27 @@
         <v>149</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F34" s="10"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="19">
+      <c r="H34" s="19">
         <v>0.125</v>
       </c>
+      <c r="I34" t="s">
+        <v>204</v>
+      </c>
       <c r="J34" t="s">
-        <v>204</v>
-      </c>
-      <c r="K34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -5634,27 +5532,24 @@
         <v>179</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F35" s="10"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="I35" t="s">
+        <v>205</v>
+      </c>
       <c r="J35" t="s">
-        <v>205</v>
-      </c>
-      <c r="K35" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -5662,30 +5557,27 @@
         <v>149</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F36" s="10"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="19">
+      <c r="H36" s="19">
         <v>0.9375</v>
       </c>
+      <c r="I36" t="s">
+        <v>207</v>
+      </c>
       <c r="J36" t="s">
-        <v>207</v>
-      </c>
-      <c r="K36" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -5693,30 +5585,27 @@
         <v>149</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F37" s="10"/>
       <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="19">
+      <c r="H37" s="19">
         <v>0.375</v>
       </c>
+      <c r="I37" t="s">
+        <v>209</v>
+      </c>
       <c r="J37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K37" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>59</v>
       </c>
@@ -5724,27 +5613,24 @@
         <v>150</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F38" s="10"/>
       <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+      <c r="I38" t="s">
+        <v>211</v>
+      </c>
       <c r="J38" t="s">
-        <v>211</v>
-      </c>
-      <c r="K38" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -5752,27 +5638,24 @@
         <v>179</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="E39" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="F39" s="10"/>
       <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="I39" t="s">
+        <v>213</v>
+      </c>
       <c r="J39" t="s">
-        <v>213</v>
-      </c>
-      <c r="K39" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -5780,28 +5663,25 @@
         <v>149</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="10" t="s">
         <v>63</v>
       </c>
+      <c r="F40" s="10"/>
       <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" t="s">
+        <v>215</v>
+      </c>
       <c r="J40" t="s">
-        <v>215</v>
-      </c>
-      <c r="K40" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -5809,27 +5689,24 @@
         <v>150</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F41" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="F41" s="10"/>
       <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
+      <c r="I41" t="s">
+        <v>217</v>
+      </c>
       <c r="J41" t="s">
-        <v>217</v>
-      </c>
-      <c r="K41" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>66</v>
       </c>
@@ -5837,30 +5714,27 @@
         <v>149</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F42" s="10"/>
       <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="19">
+      <c r="H42" s="19">
         <v>0.25</v>
       </c>
+      <c r="I42" t="s">
+        <v>219</v>
+      </c>
       <c r="J42" t="s">
-        <v>219</v>
-      </c>
-      <c r="K42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -5868,27 +5742,24 @@
         <v>150</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F43" s="10"/>
       <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+      <c r="I43" t="s">
+        <v>221</v>
+      </c>
       <c r="J43" t="s">
-        <v>221</v>
-      </c>
-      <c r="K43" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>70</v>
       </c>
@@ -5896,30 +5767,27 @@
         <v>149</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="E44" s="10" t="s">
         <v>39</v>
       </c>
+      <c r="F44" s="10"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="19">
+      <c r="H44" s="19">
         <v>0.66666666666666663</v>
       </c>
+      <c r="I44" t="s">
+        <v>223</v>
+      </c>
       <c r="J44" t="s">
-        <v>223</v>
-      </c>
-      <c r="K44" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -5927,27 +5795,24 @@
         <v>150</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F45" s="10"/>
       <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+      <c r="I45" t="s">
+        <v>225</v>
+      </c>
       <c r="J45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K45" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -5955,27 +5820,24 @@
         <v>150</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F46" s="10"/>
       <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
+      <c r="I46" t="s">
+        <v>227</v>
+      </c>
       <c r="J46" t="s">
-        <v>227</v>
-      </c>
-      <c r="K46" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -5983,27 +5845,24 @@
         <v>179</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F47" s="10"/>
       <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="I47" t="s">
+        <v>229</v>
+      </c>
       <c r="J47" t="s">
-        <v>229</v>
-      </c>
-      <c r="K47" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -6011,27 +5870,24 @@
         <v>179</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="F48" s="10"/>
       <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+      <c r="I48" t="s">
+        <v>231</v>
+      </c>
       <c r="J48" t="s">
-        <v>231</v>
-      </c>
-      <c r="K48" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>79</v>
       </c>
@@ -6039,27 +5895,24 @@
         <v>150</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F49" s="10"/>
       <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
+      <c r="I49" t="s">
+        <v>232</v>
+      </c>
       <c r="J49" t="s">
-        <v>232</v>
-      </c>
-      <c r="K49" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>80</v>
       </c>
@@ -6067,27 +5920,24 @@
         <v>179</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F50" s="10"/>
       <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
+      <c r="I50" t="s">
+        <v>233</v>
+      </c>
       <c r="J50" t="s">
-        <v>233</v>
-      </c>
-      <c r="K50" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>81</v>
       </c>
@@ -6095,30 +5945,27 @@
         <v>11</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="E51" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="F51" s="10"/>
       <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="18" t="s">
+      <c r="H51" s="18" t="s">
         <v>148</v>
       </c>
+      <c r="I51" t="s">
+        <v>235</v>
+      </c>
       <c r="J51" t="s">
-        <v>235</v>
-      </c>
-      <c r="K51" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -6126,30 +5973,27 @@
         <v>149</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F52" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="F52" s="10"/>
       <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="19">
+      <c r="H52" s="19">
         <v>0.58333333333333337</v>
       </c>
+      <c r="I52" t="s">
+        <v>236</v>
+      </c>
       <c r="J52" t="s">
-        <v>236</v>
-      </c>
-      <c r="K52" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -6157,30 +6001,27 @@
         <v>149</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F53" s="10"/>
       <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="19">
+      <c r="H53" s="19">
         <v>0.33333333333333331</v>
       </c>
+      <c r="I53" t="s">
+        <v>237</v>
+      </c>
       <c r="J53" t="s">
-        <v>237</v>
-      </c>
-      <c r="K53" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>84</v>
       </c>
@@ -6188,30 +6029,27 @@
         <v>149</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F54" s="10"/>
       <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="19">
+      <c r="H54" s="19">
         <v>0.64583333333333337</v>
       </c>
+      <c r="I54" t="s">
+        <v>238</v>
+      </c>
       <c r="J54" t="s">
-        <v>238</v>
-      </c>
-      <c r="K54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -6219,27 +6057,24 @@
         <v>179</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F55" s="10"/>
       <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="I55" t="s">
+        <v>239</v>
+      </c>
       <c r="J55" t="s">
-        <v>239</v>
-      </c>
-      <c r="K55" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -6247,27 +6082,24 @@
         <v>150</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F56" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="F56" s="10"/>
       <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+      <c r="I56" t="s">
+        <v>241</v>
+      </c>
       <c r="J56" t="s">
-        <v>241</v>
-      </c>
-      <c r="K56" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -6275,27 +6107,24 @@
         <v>179</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F57" s="10"/>
       <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
+      <c r="I57" t="s">
+        <v>243</v>
+      </c>
       <c r="J57" t="s">
-        <v>243</v>
-      </c>
-      <c r="K57" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -6303,30 +6132,27 @@
         <v>149</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F58" s="10"/>
       <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="19">
+      <c r="H58" s="19">
         <v>0.85416666666666663</v>
       </c>
+      <c r="I58" t="s">
+        <v>245</v>
+      </c>
       <c r="J58" t="s">
-        <v>245</v>
-      </c>
-      <c r="K58" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>42</v>
       </c>
@@ -6334,24 +6160,21 @@
         <v>11</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="F59" s="10"/>
       <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="18" t="s">
+      <c r="H59" s="18" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>46</v>
       </c>
@@ -6359,24 +6182,21 @@
         <v>11</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F60" s="10"/>
       <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="18" t="s">
+      <c r="H60" s="18" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>71</v>
       </c>
@@ -6384,24 +6204,21 @@
         <v>11</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F61" s="10"/>
       <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="18" t="s">
+      <c r="H61" s="18" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -6409,24 +6226,21 @@
         <v>11</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="10" t="s">
         <v>13</v>
       </c>
+      <c r="F62" s="10"/>
       <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="18" t="s">
+      <c r="H62" s="18" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -6434,21 +6248,18 @@
         <v>179</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="10" t="s">
         <v>9</v>
       </c>
+      <c r="F63" s="10"/>
       <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-    </row>
-    <row r="64" spans="1:11">
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -6456,41 +6267,38 @@
         <v>179</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="E64" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="F64" s="10"/>
       <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-    </row>
-    <row r="65" spans="1:9">
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>142</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
+      <c r="C65" t="s">
+        <v>143</v>
+      </c>
       <c r="D65" t="s">
-        <v>143</v>
-      </c>
-      <c r="E65" t="s">
         <v>11</v>
       </c>
-      <c r="I65" s="18" t="s">
+      <c r="H65" s="18" t="s">
         <v>148</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1048576" xr:uid="{44886F52-D7D0-4D08-B2D7-D1AD344D9EAF}"/>
+  <autoFilter ref="A1:H1048576" xr:uid="{44886F52-D7D0-4D08-B2D7-D1AD344D9EAF}"/>
   <hyperlinks>
-    <hyperlink ref="J7" r:id="rId1" xr:uid="{F449EA30-933C-4582-B7C5-23CD11B60575}"/>
+    <hyperlink ref="I7" r:id="rId1" xr:uid="{F449EA30-933C-4582-B7C5-23CD11B60575}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
